--- a/output/SGD_FX_Analysis_20260406.xlsx
+++ b/output/SGD_FX_Analysis_20260406.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.124</v>
+        <v>1.1255</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1.1498</v>
@@ -607,7 +607,7 @@
         <v>0.0304</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-6.46</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5.3597</v>
+        <v>5.3564</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>5.3841</v>
@@ -632,7 +632,7 @@
         <v>0.1185</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-2.96</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.6744</v>
+        <v>0.6745</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.6836</v>
@@ -657,7 +657,7 @@
         <v>0.0135</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="7">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.5881</v>
+        <v>0.5884</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.5853</v>
@@ -682,7 +682,7 @@
         <v>0.0077</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>124.206</v>
+        <v>124.345</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>112.8365</v>
+        <v>112.8367</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>124.6265</v>
@@ -704,10 +704,10 @@
         <v>98.562</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5.355</v>
+        <v>5.3554</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>14.15</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="9">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.7786</v>
+        <v>0.7784</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.7558</v>
@@ -732,7 +732,7 @@
         <v>0.0173</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
     </row>
   </sheetData>
@@ -20230,22 +20230,22 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>1.124</v>
+        <v>1.1255</v>
       </c>
       <c r="C779" t="n">
-        <v>5.3597</v>
+        <v>5.3564</v>
       </c>
       <c r="D779" t="n">
-        <v>0.6744</v>
+        <v>0.6745</v>
       </c>
       <c r="E779" t="n">
-        <v>0.5881</v>
+        <v>0.5884</v>
       </c>
       <c r="F779" t="n">
-        <v>124.206</v>
+        <v>124.345</v>
       </c>
       <c r="G779" t="n">
-        <v>0.7786</v>
+        <v>0.7784</v>
       </c>
     </row>
   </sheetData>
@@ -21215,22 +21215,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1.1249</v>
+        <v>1.1253</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.3595</v>
+        <v>5.3587</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0.6732</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.5874</v>
+        <v>0.5875</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>123.846</v>
+        <v>123.8808</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.7788</v>
+        <v>0.7786999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/SGD_FX_Analysis_20260406.xlsx
+++ b/output/SGD_FX_Analysis_20260406.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.1255</v>
+        <v>1.1256</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1.1498</v>
@@ -607,7 +607,7 @@
         <v>0.0304</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-6.34</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="5">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.6745</v>
+        <v>0.6746</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.6836</v>
@@ -657,7 +657,7 @@
         <v>0.0135</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         <v>0.0077</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="8">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>124.345</v>
+        <v>124.339</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>112.8367</v>
@@ -707,7 +707,7 @@
         <v>5.3554</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>14.28</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="9">
@@ -732,7 +732,7 @@
         <v>0.0173</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
     </row>
   </sheetData>
@@ -20230,19 +20230,19 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>1.1255</v>
+        <v>1.1256</v>
       </c>
       <c r="C779" t="n">
         <v>5.3564</v>
       </c>
       <c r="D779" t="n">
-        <v>0.6745</v>
+        <v>0.6746</v>
       </c>
       <c r="E779" t="n">
         <v>0.5884</v>
       </c>
       <c r="F779" t="n">
-        <v>124.345</v>
+        <v>124.339</v>
       </c>
       <c r="G779" t="n">
         <v>0.7784</v>
@@ -21221,13 +21221,13 @@
         <v>5.3587</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.6732</v>
+        <v>0.6733</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>0.5875</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>123.8808</v>
+        <v>123.8792</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.7786999999999999</v>
